--- a/Pathways Update/PathwaysRemove.xlsx
+++ b/Pathways Update/PathwaysRemove.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -31,118 +31,73 @@
     <t>Intake Date</t>
   </si>
   <si>
-    <t>Betty</t>
-  </si>
-  <si>
-    <t>Pickle</t>
-  </si>
-  <si>
-    <t>Crystal</t>
-  </si>
-  <si>
-    <t>Colby Jack Cheese</t>
-  </si>
-  <si>
-    <t>Sabre</t>
-  </si>
-  <si>
-    <t>Fleetwood</t>
-  </si>
-  <si>
-    <t>Mac</t>
-  </si>
-  <si>
-    <t>Bon Jovi</t>
-  </si>
-  <si>
-    <t>Tigress</t>
-  </si>
-  <si>
-    <t>Breadstick</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Maraschino</t>
-  </si>
-  <si>
-    <t>Zeke</t>
-  </si>
-  <si>
-    <t>Whiskey</t>
-  </si>
-  <si>
-    <t>Montague</t>
-  </si>
-  <si>
-    <t>Romeo</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>Ella</t>
-  </si>
-  <si>
-    <t>Casher</t>
-  </si>
-  <si>
-    <t>57237345</t>
-  </si>
-  <si>
-    <t>57091836</t>
-  </si>
-  <si>
-    <t>57091845</t>
-  </si>
-  <si>
-    <t>57670293</t>
-  </si>
-  <si>
-    <t>57305889</t>
-  </si>
-  <si>
-    <t>57657154</t>
-  </si>
-  <si>
-    <t>57657157</t>
-  </si>
-  <si>
-    <t>57657185</t>
-  </si>
-  <si>
-    <t>57657181</t>
-  </si>
-  <si>
-    <t>58011693</t>
-  </si>
-  <si>
-    <t>56455382</t>
-  </si>
-  <si>
-    <t>57954349</t>
-  </si>
-  <si>
-    <t>57925440</t>
-  </si>
-  <si>
-    <t>57935094</t>
-  </si>
-  <si>
-    <t>57765213</t>
-  </si>
-  <si>
-    <t>57765219</t>
-  </si>
-  <si>
-    <t>57945726</t>
-  </si>
-  <si>
-    <t>57945729</t>
-  </si>
-  <si>
-    <t>58057188</t>
+    <t>PISHU</t>
+  </si>
+  <si>
+    <t>ZOEY</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>OCEAN</t>
+  </si>
+  <si>
+    <t>PIGGY STARDUST</t>
+  </si>
+  <si>
+    <t>TINK</t>
+  </si>
+  <si>
+    <t>Gengar</t>
+  </si>
+  <si>
+    <t>Lucario</t>
+  </si>
+  <si>
+    <t>MEW</t>
+  </si>
+  <si>
+    <t>CHERRY CHEESECAKE</t>
+  </si>
+  <si>
+    <t>LEROY</t>
+  </si>
+  <si>
+    <t>58227600</t>
+  </si>
+  <si>
+    <t>58415270</t>
+  </si>
+  <si>
+    <t>58047453</t>
+  </si>
+  <si>
+    <t>58467665</t>
+  </si>
+  <si>
+    <t>58480470</t>
+  </si>
+  <si>
+    <t>58571051</t>
+  </si>
+  <si>
+    <t>58273702</t>
+  </si>
+  <si>
+    <t>58096300</t>
+  </si>
+  <si>
+    <t>58096304</t>
+  </si>
+  <si>
+    <t>58096303</t>
+  </si>
+  <si>
+    <t>58501234</t>
+  </si>
+  <si>
+    <t>58580905</t>
   </si>
   <si>
     <t>Cat</t>
@@ -151,70 +106,64 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>Rabbit</t>
+  </si>
+  <si>
     <t>Bird</t>
   </si>
   <si>
-    <t>Cat Room G</t>
-  </si>
-  <si>
-    <t>Feature Room 1</t>
-  </si>
-  <si>
-    <t>Dog A</t>
+    <t>Rodent</t>
+  </si>
+  <si>
+    <t>Reptile/Amphibian</t>
   </si>
   <si>
     <t>Foster Home</t>
   </si>
   <si>
-    <t>Condo Rooms</t>
-  </si>
-  <si>
     <t>Small Animals &amp; Exotics</t>
   </si>
   <si>
-    <t>Cat Room H</t>
-  </si>
-  <si>
-    <t>Dog B</t>
-  </si>
-  <si>
-    <t>Dog F</t>
-  </si>
-  <si>
-    <t>11/8/2024</t>
-  </si>
-  <si>
-    <t>10/22/2024</t>
-  </si>
-  <si>
-    <t>1/17/2025</t>
-  </si>
-  <si>
-    <t>11/21/2024</t>
-  </si>
-  <si>
-    <t>1/16/2025</t>
-  </si>
-  <si>
-    <t>3/13/2025</t>
-  </si>
-  <si>
-    <t>1/29/2025</t>
-  </si>
-  <si>
-    <t>3/4/2025</t>
-  </si>
-  <si>
-    <t>2/28/2025</t>
-  </si>
-  <si>
-    <t>2/1/2025</t>
-  </si>
-  <si>
-    <t>3/3/2025</t>
+    <t>Cat Adoption</t>
+  </si>
+  <si>
+    <t>Foster Care Room</t>
+  </si>
+  <si>
+    <t>ICU</t>
+  </si>
+  <si>
+    <t>Dog Adoptions C</t>
+  </si>
+  <si>
+    <t>4/1/2025</t>
+  </si>
+  <si>
+    <t>5/1/2025</t>
   </si>
   <si>
     <t>3/21/2025</t>
+  </si>
+  <si>
+    <t>5/9/2025</t>
+  </si>
+  <si>
+    <t>5/12/2025</t>
+  </si>
+  <si>
+    <t>5/24/2025</t>
+  </si>
+  <si>
+    <t>4/15/2025</t>
+  </si>
+  <si>
+    <t>3/28/2025</t>
+  </si>
+  <si>
+    <t>5/14/2025</t>
+  </si>
+  <si>
+    <t>5/27/2025</t>
   </si>
 </sst>
 </file>
@@ -572,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -597,16 +546,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -614,305 +563,183 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
       <c r="E13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Pathways Update/PathwaysRemove.xlsx
+++ b/Pathways Update/PathwaysRemove.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -31,73 +31,37 @@
     <t>Intake Date</t>
   </si>
   <si>
-    <t>PISHU</t>
-  </si>
-  <si>
-    <t>ZOEY</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>OCEAN</t>
-  </si>
-  <si>
-    <t>PIGGY STARDUST</t>
-  </si>
-  <si>
-    <t>TINK</t>
-  </si>
-  <si>
-    <t>Gengar</t>
-  </si>
-  <si>
-    <t>Lucario</t>
-  </si>
-  <si>
-    <t>MEW</t>
-  </si>
-  <si>
-    <t>CHERRY CHEESECAKE</t>
-  </si>
-  <si>
-    <t>LEROY</t>
-  </si>
-  <si>
-    <t>58227600</t>
-  </si>
-  <si>
-    <t>58415270</t>
-  </si>
-  <si>
-    <t>58047453</t>
-  </si>
-  <si>
-    <t>58467665</t>
-  </si>
-  <si>
-    <t>58480470</t>
-  </si>
-  <si>
-    <t>58571051</t>
-  </si>
-  <si>
-    <t>58273702</t>
-  </si>
-  <si>
-    <t>58096300</t>
-  </si>
-  <si>
-    <t>58096304</t>
-  </si>
-  <si>
-    <t>58096303</t>
-  </si>
-  <si>
-    <t>58501234</t>
-  </si>
-  <si>
-    <t>58580905</t>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>SAMMY</t>
+  </si>
+  <si>
+    <t>MAMA MIA</t>
+  </si>
+  <si>
+    <t>Clefairy</t>
+  </si>
+  <si>
+    <t>Rosie</t>
+  </si>
+  <si>
+    <t>57782868</t>
+  </si>
+  <si>
+    <t>58018420</t>
+  </si>
+  <si>
+    <t>58248928</t>
+  </si>
+  <si>
+    <t>58096299</t>
+  </si>
+  <si>
+    <t>58231395</t>
+  </si>
+  <si>
+    <t>58231399</t>
   </si>
   <si>
     <t>Cat</t>
@@ -106,64 +70,28 @@
     <t>Dog</t>
   </si>
   <si>
-    <t>Rabbit</t>
-  </si>
-  <si>
-    <t>Bird</t>
-  </si>
-  <si>
-    <t>Rodent</t>
-  </si>
-  <si>
-    <t>Reptile/Amphibian</t>
-  </si>
-  <si>
-    <t>Foster Home</t>
-  </si>
-  <si>
-    <t>Small Animals &amp; Exotics</t>
-  </si>
-  <si>
-    <t>Cat Adoption</t>
-  </si>
-  <si>
-    <t>Foster Care Room</t>
-  </si>
-  <si>
-    <t>ICU</t>
-  </si>
-  <si>
-    <t>Dog Adoptions C</t>
-  </si>
-  <si>
-    <t>4/1/2025</t>
-  </si>
-  <si>
-    <t>5/1/2025</t>
-  </si>
-  <si>
-    <t>3/21/2025</t>
-  </si>
-  <si>
-    <t>5/9/2025</t>
-  </si>
-  <si>
-    <t>5/12/2025</t>
-  </si>
-  <si>
-    <t>5/24/2025</t>
-  </si>
-  <si>
-    <t>4/15/2025</t>
+    <t>If The Fur Fits</t>
+  </si>
+  <si>
+    <t>Cat Adoption Condo Rooms</t>
+  </si>
+  <si>
+    <t>Cat Room H</t>
+  </si>
+  <si>
+    <t>2/20/2025</t>
+  </si>
+  <si>
+    <t>4/3/2025</t>
+  </si>
+  <si>
+    <t>4/14/2025</t>
   </si>
   <si>
     <t>3/28/2025</t>
   </si>
   <si>
-    <t>5/14/2025</t>
-  </si>
-  <si>
-    <t>5/27/2025</t>
+    <t>4/2/2025</t>
   </si>
 </sst>
 </file>
@@ -521,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -546,16 +474,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -563,64 +491,64 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -628,118 +556,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Pathways Update/PathwaysRemove.xlsx
+++ b/Pathways Update/PathwaysRemove.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -31,37 +31,70 @@
     <t>Intake Date</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>SAMMY</t>
-  </si>
-  <si>
-    <t>MAMA MIA</t>
-  </si>
-  <si>
-    <t>Clefairy</t>
-  </si>
-  <si>
-    <t>Rosie</t>
-  </si>
-  <si>
-    <t>57782868</t>
-  </si>
-  <si>
-    <t>58018420</t>
-  </si>
-  <si>
-    <t>58248928</t>
-  </si>
-  <si>
-    <t>58096299</t>
-  </si>
-  <si>
-    <t>58231395</t>
-  </si>
-  <si>
-    <t>58231399</t>
+    <t>PALM</t>
+  </si>
+  <si>
+    <t>COLLIE</t>
+  </si>
+  <si>
+    <t>SPECK</t>
+  </si>
+  <si>
+    <t>LAUREL</t>
+  </si>
+  <si>
+    <t>Gyarados</t>
+  </si>
+  <si>
+    <t>Mochi</t>
+  </si>
+  <si>
+    <t>SUDS</t>
+  </si>
+  <si>
+    <t>Beau</t>
+  </si>
+  <si>
+    <t>RAYNE</t>
+  </si>
+  <si>
+    <t>HEATH</t>
+  </si>
+  <si>
+    <t>MARINA</t>
+  </si>
+  <si>
+    <t>58262248</t>
+  </si>
+  <si>
+    <t>57884999</t>
+  </si>
+  <si>
+    <t>52249653</t>
+  </si>
+  <si>
+    <t>58289985</t>
+  </si>
+  <si>
+    <t>58096306</t>
+  </si>
+  <si>
+    <t>58353916</t>
+  </si>
+  <si>
+    <t>58598619</t>
+  </si>
+  <si>
+    <t>58677023</t>
+  </si>
+  <si>
+    <t>57710656</t>
+  </si>
+  <si>
+    <t>58654173</t>
+  </si>
+  <si>
+    <t>58706705</t>
   </si>
   <si>
     <t>Cat</t>
@@ -70,28 +103,64 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>Rabbit</t>
+  </si>
+  <si>
+    <t>Feature Room 2</t>
+  </si>
+  <si>
     <t>If The Fur Fits</t>
   </si>
   <si>
+    <t>Dog Adoptions D</t>
+  </si>
+  <si>
     <t>Cat Adoption Condo Rooms</t>
   </si>
   <si>
-    <t>Cat Room H</t>
+    <t>Cat Treatment</t>
+  </si>
+  <si>
+    <t>Offsite Adoptions</t>
+  </si>
+  <si>
+    <t>Dog Adoptions A</t>
+  </si>
+  <si>
+    <t>Dog Adoptions C</t>
+  </si>
+  <si>
+    <t>Adoptions Lobby</t>
+  </si>
+  <si>
+    <t>4/8/2025</t>
   </si>
   <si>
     <t>2/20/2025</t>
   </si>
   <si>
-    <t>4/3/2025</t>
-  </si>
-  <si>
-    <t>4/14/2025</t>
+    <t>4/16/2025</t>
+  </si>
+  <si>
+    <t>4/11/2025</t>
   </si>
   <si>
     <t>3/28/2025</t>
   </si>
   <si>
-    <t>4/2/2025</t>
+    <t>4/22/2025</t>
+  </si>
+  <si>
+    <t>5/29/2025</t>
+  </si>
+  <si>
+    <t>6/10/2025</t>
+  </si>
+  <si>
+    <t>6/13/2025</t>
+  </si>
+  <si>
+    <t>6/6/2025</t>
   </si>
 </sst>
 </file>
@@ -449,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -474,16 +543,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -491,16 +560,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -508,16 +577,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -525,47 +594,135 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
